--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.50276913560943</v>
+        <v>5.606699984536533</v>
       </c>
       <c r="D2" t="n">
-        <v>34.24892368714784</v>
+        <v>5.565450099161524</v>
       </c>
       <c r="E2" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F2" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.33760400149149</v>
+        <v>6.067360650242367</v>
       </c>
       <c r="D3" t="n">
-        <v>18.83750135266772</v>
+        <v>3.061093969808505</v>
       </c>
       <c r="E3" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F3" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.59986657355626</v>
+        <v>7.409978318202893</v>
       </c>
       <c r="D4" t="n">
-        <v>26.66530196232484</v>
+        <v>4.333111568877787</v>
       </c>
       <c r="E4" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F4" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.55569926820554</v>
+        <v>2.8528011310834</v>
       </c>
       <c r="D5" t="n">
-        <v>16.96875055675725</v>
+        <v>2.757421965473053</v>
       </c>
       <c r="E5" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F5" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.26234237086079</v>
+        <v>6.380130635264878</v>
       </c>
       <c r="D6" t="n">
-        <v>10.64657212904563</v>
+        <v>1.730067970969915</v>
       </c>
       <c r="E6" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F6" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.66743852372556</v>
+        <v>7.583458760105405</v>
       </c>
       <c r="D7" t="n">
-        <v>2.867887150999365</v>
+        <v>0.4660316620373968</v>
       </c>
       <c r="E7" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F7" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.87566846180112</v>
+        <v>6.967296125042682</v>
       </c>
       <c r="D8" t="n">
-        <v>23.72715812902629</v>
+        <v>3.855663195966772</v>
       </c>
       <c r="E8" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F8" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.65074299620852</v>
+        <v>4.980745736883885</v>
       </c>
       <c r="D9" t="n">
-        <v>21.13199551788475</v>
+        <v>3.433949271656273</v>
       </c>
       <c r="E9" t="n">
-        <v>8.884700981832788</v>
+        <v>1.443763909547828</v>
       </c>
       <c r="F9" t="n">
-        <v>9.021907257078015</v>
+        <v>1.466059929275177</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
